--- a/Contrato de Intermediação (3).xlsx
+++ b/Contrato de Intermediação (3).xlsx
@@ -2015,16 +2015,8 @@
       <c r="B58" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="32" t="str">
-        <f>IF(#REF!="","",#REF!)</f>
-        <v>#REF!</v>
-      </c>
       <c r="I58" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="J58" s="32" t="str">
-        <f>IF(#REF!="","",#REF!)</f>
-        <v>#REF!</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
